--- a/research/traditional_assets/database/data/malaysia/malaysia_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_insurance_general.xlsx
@@ -588,49 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.051</v>
+        <v>0.0436</v>
       </c>
       <c r="E2">
-        <v>0.12145</v>
-      </c>
-      <c r="F2">
-        <v>0.062</v>
+        <v>0.12865</v>
       </c>
       <c r="G2">
-        <v>0.1526466728236038</v>
+        <v>0.1412904892287028</v>
       </c>
       <c r="H2">
-        <v>0.1526466728236038</v>
+        <v>0.1412904892287028</v>
       </c>
       <c r="I2">
-        <v>0.1207116123073932</v>
+        <v>0.122431161853593</v>
       </c>
       <c r="J2">
-        <v>0.08529304158525114</v>
+        <v>0.1029323318909316</v>
       </c>
       <c r="K2">
-        <v>197.159</v>
+        <v>175.1</v>
       </c>
       <c r="L2">
-        <v>0.09583385991347883</v>
+        <v>0.090458232164075</v>
       </c>
       <c r="M2">
-        <v>45.40000000000001</v>
+        <v>43.7</v>
       </c>
       <c r="N2">
-        <v>0.03321870198287847</v>
+        <v>0.03395229585890763</v>
       </c>
       <c r="O2">
-        <v>0.2302709995485877</v>
+        <v>0.249571673329526</v>
       </c>
       <c r="P2">
-        <v>45.40000000000001</v>
+        <v>43.7</v>
       </c>
       <c r="Q2">
-        <v>0.03321870198287847</v>
+        <v>0.03395229585890763</v>
       </c>
       <c r="R2">
-        <v>0.2302709995485877</v>
+        <v>0.249571673329526</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>477.5</v>
+        <v>728.51</v>
       </c>
       <c r="V2">
-        <v>0.3493817223970147</v>
+        <v>0.5660088571206588</v>
       </c>
       <c r="W2">
-        <v>0.1298143851508121</v>
+        <v>0.1115735012934428</v>
       </c>
       <c r="X2">
-        <v>0.05270962652048752</v>
+        <v>0.08798574625341071</v>
       </c>
       <c r="Y2">
-        <v>0.07710475863032454</v>
+        <v>0.02358775504003209</v>
       </c>
       <c r="Z2">
-        <v>1.816953403751722</v>
+        <v>1.762054786913987</v>
       </c>
       <c r="AA2">
-        <v>0.1452944944399461</v>
+        <v>0.1327132031594563</v>
       </c>
       <c r="AB2">
-        <v>0.0523552761274713</v>
+        <v>0.08762650768902425</v>
       </c>
       <c r="AC2">
-        <v>0.09293921831247481</v>
+        <v>0.04508669547043204</v>
       </c>
       <c r="AD2">
-        <v>8.527000000000001</v>
+        <v>5.901999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8.527000000000001</v>
+        <v>5.901999999999999</v>
       </c>
       <c r="AG2">
-        <v>-468.973</v>
+        <v>-722.6079999999999</v>
       </c>
       <c r="AH2">
-        <v>0.006200430910678747</v>
+        <v>0.004564571439177974</v>
       </c>
       <c r="AI2">
-        <v>0.005250205187155931</v>
+        <v>0.00393361245852778</v>
       </c>
       <c r="AJ2">
-        <v>-0.5224004625014063</v>
+        <v>-1.280103172409883</v>
       </c>
       <c r="AK2">
-        <v>-0.4090022300190036</v>
+        <v>-0.9361516896146092</v>
       </c>
       <c r="AL2">
-        <v>0.715</v>
+        <v>0.418</v>
       </c>
       <c r="AM2">
-        <v>0.715</v>
+        <v>0.418</v>
       </c>
       <c r="AN2">
-        <v>0.03184211509018261</v>
+        <v>0.02308986346387074</v>
       </c>
       <c r="AO2">
-        <v>347.3286713286714</v>
+        <v>566.9617224880383</v>
       </c>
       <c r="AP2">
-        <v>-1.751271518727361</v>
+        <v>-2.826994249051289</v>
       </c>
       <c r="AQ2">
-        <v>347.3286713286714</v>
+        <v>566.9617224880383</v>
       </c>
     </row>
     <row r="3">
@@ -725,49 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09130000000000001</v>
+        <v>0.0989</v>
       </c>
       <c r="E3">
-        <v>0.156</v>
-      </c>
-      <c r="F3">
-        <v>0.062</v>
+        <v>0.161</v>
       </c>
       <c r="G3">
-        <v>0.1822284469343293</v>
+        <v>0.180647140009201</v>
       </c>
       <c r="H3">
-        <v>0.1822284469343293</v>
+        <v>0.180647140009201</v>
       </c>
       <c r="I3">
-        <v>0.15406162464986</v>
+        <v>0.1669989265450084</v>
       </c>
       <c r="J3">
-        <v>0.1331377621471124</v>
+        <v>0.1319138309681213</v>
       </c>
       <c r="K3">
-        <v>85.7</v>
+        <v>86</v>
       </c>
       <c r="L3">
-        <v>0.1333644568938687</v>
+        <v>0.1318816132495016</v>
       </c>
       <c r="M3">
-        <v>23.8</v>
+        <v>21.6</v>
       </c>
       <c r="N3">
-        <v>0.03207114944077617</v>
+        <v>0.03284671532846715</v>
       </c>
       <c r="O3">
-        <v>0.2777129521586931</v>
+        <v>0.2511627906976744</v>
       </c>
       <c r="P3">
-        <v>23.8</v>
+        <v>21.6</v>
       </c>
       <c r="Q3">
-        <v>0.03207114944077617</v>
+        <v>0.03284671532846715</v>
       </c>
       <c r="R3">
-        <v>0.2777129521586931</v>
+        <v>0.2511627906976744</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,55 +770,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>189.6</v>
+        <v>333.3</v>
       </c>
       <c r="V3">
-        <v>0.2554911736962673</v>
+        <v>0.5068430656934306</v>
       </c>
       <c r="W3">
-        <v>0.2368057474440453</v>
+        <v>0.2049082678103407</v>
       </c>
       <c r="X3">
-        <v>0.05234217791192801</v>
+        <v>0.08766392288555866</v>
       </c>
       <c r="Y3">
-        <v>0.1844635695321173</v>
+        <v>0.1172443449247821</v>
       </c>
       <c r="Z3">
-        <v>2.714484856165252</v>
+        <v>2.832052880042735</v>
       </c>
       <c r="AA3">
-        <v>0.3614004391320678</v>
+        <v>0.3735869449107386</v>
       </c>
       <c r="AB3">
-        <v>0.05233650077480251</v>
+        <v>0.08765596631202587</v>
       </c>
       <c r="AC3">
-        <v>0.3090639383572653</v>
+        <v>0.2859309785987127</v>
       </c>
       <c r="AD3">
-        <v>0.157</v>
+        <v>0.129</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.157</v>
+        <v>0.129</v>
       </c>
       <c r="AG3">
-        <v>-189.443</v>
+        <v>-333.171</v>
       </c>
       <c r="AH3">
-        <v>0.0002115170352047875</v>
+        <v>0.0001961294089206953</v>
       </c>
       <c r="AI3">
-        <v>0.0003670308142239636</v>
+        <v>0.0002938971906618154</v>
       </c>
       <c r="AJ3">
-        <v>-0.3427858508984777</v>
+        <v>-1.026945803242004</v>
       </c>
       <c r="AK3">
-        <v>-0.7954542591651723</v>
+        <v>-3.154162209241779</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -833,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.001409335727109515</v>
+        <v>0.001067880794701987</v>
       </c>
       <c r="AP3">
-        <v>-1.70056552962298</v>
+        <v>-2.758038079470199</v>
       </c>
     </row>
     <row r="4">
@@ -856,46 +850,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.051</v>
+        <v>0.0436</v>
       </c>
       <c r="E4">
-        <v>0.08689999999999999</v>
+        <v>0.09630000000000001</v>
       </c>
       <c r="G4">
-        <v>0.1383689348895251</v>
+        <v>0.127922184077162</v>
       </c>
       <c r="H4">
-        <v>0.1383689348895251</v>
+        <v>0.127922184077162</v>
       </c>
       <c r="I4">
-        <v>0.1088600161491595</v>
+        <v>0.1108386463952918</v>
       </c>
       <c r="J4">
-        <v>0.08225142341047231</v>
+        <v>0.08116723884256988</v>
       </c>
       <c r="K4">
-        <v>111.9</v>
+        <v>99.2</v>
       </c>
       <c r="L4">
-        <v>0.08214049768773399</v>
+        <v>0.08108549942782409</v>
       </c>
       <c r="M4">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="N4">
-        <v>0.03942325241832451</v>
+        <v>0.03840806395550921</v>
       </c>
       <c r="O4">
-        <v>0.193029490616622</v>
+        <v>0.2227822580645161</v>
       </c>
       <c r="P4">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="Q4">
-        <v>0.03942325241832451</v>
+        <v>0.03840806395550921</v>
       </c>
       <c r="R4">
-        <v>0.193029490616622</v>
+        <v>0.2227822580645161</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,73 +898,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>276.4</v>
+        <v>387.6</v>
       </c>
       <c r="V4">
-        <v>0.50447161890856</v>
+        <v>0.6736183524504693</v>
       </c>
       <c r="W4">
-        <v>0.1298143851508121</v>
+        <v>0.1115735012934428</v>
       </c>
       <c r="X4">
-        <v>0.05270962652048752</v>
+        <v>0.08798574625341071</v>
       </c>
       <c r="Y4">
-        <v>0.07710475863032454</v>
+        <v>0.02358775504003209</v>
       </c>
       <c r="Z4">
-        <v>1.766467842323651</v>
+        <v>1.635058738623151</v>
       </c>
       <c r="AA4">
-        <v>0.1452944944399461</v>
+        <v>0.1327132031594563</v>
       </c>
       <c r="AB4">
-        <v>0.0523552761274713</v>
+        <v>0.08762650768902425</v>
       </c>
       <c r="AC4">
-        <v>0.09293921831247481</v>
+        <v>0.04508669547043204</v>
       </c>
       <c r="AD4">
-        <v>7.23</v>
+        <v>5.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>7.23</v>
+        <v>5.1</v>
       </c>
       <c r="AG4">
-        <v>-269.17</v>
+        <v>-382.5</v>
       </c>
       <c r="AH4">
-        <v>0.01302397636589628</v>
+        <v>0.008785529715762273</v>
       </c>
       <c r="AI4">
-        <v>0.007056205654724146</v>
+        <v>0.00550577566663068</v>
       </c>
       <c r="AJ4">
-        <v>-0.9657015750008967</v>
+        <v>-1.98289269051322</v>
       </c>
       <c r="AK4">
-        <v>-0.3597423252208545</v>
+        <v>-0.7100426953777612</v>
       </c>
       <c r="AL4">
-        <v>0.637</v>
+        <v>0.37</v>
       </c>
       <c r="AM4">
-        <v>0.637</v>
+        <v>0.37</v>
       </c>
       <c r="AN4">
-        <v>0.04670542635658915</v>
+        <v>0.03596614950634696</v>
       </c>
       <c r="AO4">
-        <v>232.8100470957614</v>
+        <v>366.4864864864865</v>
       </c>
       <c r="AP4">
-        <v>-1.738824289405684</v>
+        <v>-2.697461212976022</v>
       </c>
       <c r="AQ4">
-        <v>232.8100470957614</v>
+        <v>366.4864864864865</v>
       </c>
     </row>
     <row r="5">
@@ -990,25 +984,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.111</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="G5">
-        <v>0.1610687022900763</v>
+        <v>-0.01335548172757475</v>
       </c>
       <c r="H5">
-        <v>0.1610687022900763</v>
+        <v>-0.01335548172757475</v>
       </c>
       <c r="I5">
-        <v>0.01984732824427481</v>
+        <v>-0.124750830564784</v>
       </c>
       <c r="J5">
-        <v>0.009923664122137405</v>
+        <v>-0.124750830564784</v>
       </c>
       <c r="K5">
-        <v>-0.441</v>
+        <v>-10.1</v>
       </c>
       <c r="L5">
-        <v>-0.008416030534351145</v>
+        <v>-0.1677740863787375</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1032,73 +1026,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>11.5</v>
+        <v>7.61</v>
       </c>
       <c r="V5">
-        <v>0.1499348109517601</v>
+        <v>0.1406654343807763</v>
       </c>
       <c r="W5">
-        <v>-0.003197969543147208</v>
+        <v>-0.07415565345080764</v>
       </c>
       <c r="X5">
-        <v>0.05275680927610681</v>
+        <v>0.08811854642902416</v>
       </c>
       <c r="Y5">
-        <v>-0.05595477881925402</v>
+        <v>-0.1622741998798318</v>
       </c>
       <c r="Z5">
-        <v>0.4213912344189787</v>
+        <v>0.5014159586873231</v>
       </c>
       <c r="AA5">
-        <v>0.004181745074386812</v>
+        <v>-0.06255205730468101</v>
       </c>
       <c r="AB5">
-        <v>0.05235765219732767</v>
+        <v>0.08761449861728104</v>
       </c>
       <c r="AC5">
-        <v>-0.04817590712294086</v>
+        <v>-0.150166555921962</v>
       </c>
       <c r="AD5">
-        <v>1.14</v>
+        <v>0.673</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.14</v>
+        <v>0.673</v>
       </c>
       <c r="AG5">
-        <v>-10.36</v>
+        <v>-6.937</v>
       </c>
       <c r="AH5">
-        <v>0.01464542651593011</v>
+        <v>0.01228707574900042</v>
       </c>
       <c r="AI5">
-        <v>0.006637941073716082</v>
+        <v>0.004978804938856132</v>
       </c>
       <c r="AJ5">
-        <v>-0.1561652095266807</v>
+        <v>-0.1470856391662956</v>
       </c>
       <c r="AK5">
-        <v>-0.06465302046929605</v>
+        <v>-0.05438097253905913</v>
       </c>
       <c r="AL5">
-        <v>0.078</v>
+        <v>0.048</v>
       </c>
       <c r="AM5">
-        <v>0.078</v>
+        <v>0.048</v>
       </c>
       <c r="AN5">
-        <v>0.7169811320754716</v>
+        <v>-0.09628040057224607</v>
       </c>
       <c r="AO5">
-        <v>13.33333333333333</v>
+        <v>-156.4583333333333</v>
       </c>
       <c r="AP5">
-        <v>-6.515723270440251</v>
+        <v>0.99241773962804</v>
       </c>
       <c r="AQ5">
-        <v>13.33333333333333</v>
+        <v>-156.4583333333333</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/malaysia/malaysia_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/malaysia/malaysia_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0436</v>
+        <v>0.0696</v>
       </c>
       <c r="E2">
-        <v>0.12865</v>
+        <v>0.078</v>
       </c>
       <c r="G2">
-        <v>0.1412904892287028</v>
+        <v>0.1315734089765292</v>
       </c>
       <c r="H2">
-        <v>0.1412904892287028</v>
+        <v>0.1315734089765292</v>
       </c>
       <c r="I2">
-        <v>0.122431161853593</v>
+        <v>0.1337420506016379</v>
       </c>
       <c r="J2">
-        <v>0.1029323318909316</v>
+        <v>0.09548175695071108</v>
       </c>
       <c r="K2">
-        <v>175.1</v>
+        <v>205.87</v>
       </c>
       <c r="L2">
-        <v>0.090458232164075</v>
+        <v>0.09418950450656541</v>
       </c>
       <c r="M2">
-        <v>43.7</v>
+        <v>54</v>
       </c>
       <c r="N2">
-        <v>0.03395229585890763</v>
+        <v>0.0370802719219941</v>
       </c>
       <c r="O2">
-        <v>0.249571673329526</v>
+        <v>0.2623014523728566</v>
       </c>
       <c r="P2">
-        <v>43.7</v>
+        <v>54</v>
       </c>
       <c r="Q2">
-        <v>0.03395229585890763</v>
+        <v>0.0370802719219941</v>
       </c>
       <c r="R2">
-        <v>0.249571673329526</v>
+        <v>0.2623014523728566</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>728.51</v>
+        <v>347.89</v>
       </c>
       <c r="V2">
-        <v>0.5660088571206588</v>
+        <v>0.2388862184989357</v>
       </c>
       <c r="W2">
-        <v>0.1115735012934428</v>
+        <v>0.1506203473945409</v>
       </c>
       <c r="X2">
-        <v>0.08798574625341071</v>
+        <v>0.07861655276038142</v>
       </c>
       <c r="Y2">
-        <v>0.02358775504003209</v>
+        <v>0.07200379463415953</v>
       </c>
       <c r="Z2">
-        <v>1.762054786913987</v>
+        <v>2.966911545123335</v>
       </c>
       <c r="AA2">
-        <v>0.1327132031594563</v>
+        <v>0.2228575899050291</v>
       </c>
       <c r="AB2">
-        <v>0.08762650768902425</v>
+        <v>0.07831102458348477</v>
       </c>
       <c r="AC2">
-        <v>0.04508669547043204</v>
+        <v>0.1445465653215443</v>
       </c>
       <c r="AD2">
-        <v>5.901999999999999</v>
+        <v>8.695</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.901999999999999</v>
+        <v>8.695</v>
       </c>
       <c r="AG2">
-        <v>-722.6079999999999</v>
+        <v>-339.195</v>
       </c>
       <c r="AH2">
-        <v>0.004564571439177974</v>
+        <v>0.005935173840183755</v>
       </c>
       <c r="AI2">
-        <v>0.00393361245852778</v>
+        <v>0.005408027764733688</v>
       </c>
       <c r="AJ2">
-        <v>-1.280103172409883</v>
+        <v>-0.3036375273586637</v>
       </c>
       <c r="AK2">
-        <v>-0.9361516896146092</v>
+        <v>-0.2692226794877391</v>
       </c>
       <c r="AL2">
-        <v>0.418</v>
+        <v>0.044</v>
       </c>
       <c r="AM2">
-        <v>0.418</v>
+        <v>-1.696</v>
       </c>
       <c r="AN2">
-        <v>0.02308986346387074</v>
+        <v>0.02799420476497102</v>
       </c>
       <c r="AO2">
-        <v>566.9617224880383</v>
+        <v>6643.636363636364</v>
       </c>
       <c r="AP2">
-        <v>-2.826994249051289</v>
+        <v>-1.092063747585319</v>
       </c>
       <c r="AQ2">
-        <v>566.9617224880383</v>
+        <v>-172.3584905660377</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0989</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="E3">
-        <v>0.161</v>
+        <v>0.078</v>
       </c>
       <c r="G3">
-        <v>0.180647140009201</v>
+        <v>0.1769899103139013</v>
       </c>
       <c r="H3">
-        <v>0.180647140009201</v>
+        <v>0.1769899103139013</v>
       </c>
       <c r="I3">
-        <v>0.1669989265450084</v>
+        <v>0.1674607623318386</v>
       </c>
       <c r="J3">
-        <v>0.1319138309681213</v>
+        <v>0.113130289815504</v>
       </c>
       <c r="K3">
-        <v>86</v>
+        <v>80.8</v>
       </c>
       <c r="L3">
-        <v>0.1318816132495016</v>
+        <v>0.1132286995515695</v>
       </c>
       <c r="M3">
-        <v>21.6</v>
+        <v>24.1</v>
       </c>
       <c r="N3">
-        <v>0.03284671532846715</v>
+        <v>0.03568784244039686</v>
       </c>
       <c r="O3">
-        <v>0.2511627906976744</v>
+        <v>0.2982673267326733</v>
       </c>
       <c r="P3">
-        <v>21.6</v>
+        <v>24.1</v>
       </c>
       <c r="Q3">
-        <v>0.03284671532846715</v>
+        <v>0.03568784244039686</v>
       </c>
       <c r="R3">
-        <v>0.2511627906976744</v>
+        <v>0.2982673267326733</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,55 +770,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>333.3</v>
+        <v>188.9</v>
       </c>
       <c r="V3">
-        <v>0.5068430656934306</v>
+        <v>0.2797275285058493</v>
       </c>
       <c r="W3">
-        <v>0.2049082678103407</v>
+        <v>0.1872971719981456</v>
       </c>
       <c r="X3">
-        <v>0.08766392288555866</v>
+        <v>0.07835234175330948</v>
       </c>
       <c r="Y3">
-        <v>0.1172443449247821</v>
+        <v>0.1089448302448361</v>
       </c>
       <c r="Z3">
-        <v>2.832052880042735</v>
+        <v>7.264657076830672</v>
       </c>
       <c r="AA3">
-        <v>0.3735869449107386</v>
+        <v>0.8218527605121058</v>
       </c>
       <c r="AB3">
-        <v>0.08765596631202587</v>
+        <v>0.07834702593233862</v>
       </c>
       <c r="AC3">
-        <v>0.2859309785987127</v>
+        <v>0.7435057345797671</v>
       </c>
       <c r="AD3">
-        <v>0.129</v>
+        <v>0.105</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.129</v>
+        <v>0.105</v>
       </c>
       <c r="AG3">
-        <v>-333.171</v>
+        <v>-188.795</v>
       </c>
       <c r="AH3">
-        <v>0.0001961294089206953</v>
+        <v>0.0001554622781886424</v>
       </c>
       <c r="AI3">
-        <v>0.0002938971906618154</v>
+        <v>0.0002820268328386672</v>
       </c>
       <c r="AJ3">
-        <v>-1.026945803242004</v>
+        <v>-0.38806384312597</v>
       </c>
       <c r="AK3">
-        <v>-3.154162209241779</v>
+        <v>-1.029388511763583</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -827,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>0.001067880794701987</v>
+        <v>0.0008015267175572519</v>
       </c>
       <c r="AP3">
-        <v>-2.758038079470199</v>
+        <v>-1.44118320610687</v>
       </c>
     </row>
     <row r="4">
@@ -850,46 +850,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0436</v>
+        <v>0.0696</v>
       </c>
       <c r="E4">
-        <v>0.09630000000000001</v>
+        <v>0.09390000000000001</v>
       </c>
       <c r="G4">
-        <v>0.127922184077162</v>
+        <v>0.1190956221198157</v>
       </c>
       <c r="H4">
-        <v>0.127922184077162</v>
+        <v>0.1190956221198157</v>
       </c>
       <c r="I4">
-        <v>0.1108386463952918</v>
+        <v>0.1199596774193548</v>
       </c>
       <c r="J4">
-        <v>0.08116723884256988</v>
+        <v>0.0864279218914521</v>
       </c>
       <c r="K4">
-        <v>99.2</v>
+        <v>121.4</v>
       </c>
       <c r="L4">
-        <v>0.08108549942782409</v>
+        <v>0.0874135944700461</v>
       </c>
       <c r="M4">
-        <v>22.1</v>
+        <v>29.9</v>
       </c>
       <c r="N4">
-        <v>0.03840806395550921</v>
+        <v>0.04179480011182555</v>
       </c>
       <c r="O4">
-        <v>0.2227822580645161</v>
+        <v>0.2462932454695222</v>
       </c>
       <c r="P4">
-        <v>22.1</v>
+        <v>29.9</v>
       </c>
       <c r="Q4">
-        <v>0.03840806395550921</v>
+        <v>0.04179480011182555</v>
       </c>
       <c r="R4">
-        <v>0.2227822580645161</v>
+        <v>0.2462932454695222</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,73 +898,70 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>387.6</v>
+        <v>155.6</v>
       </c>
       <c r="V4">
-        <v>0.6736183524504693</v>
+        <v>0.2175006989097009</v>
       </c>
       <c r="W4">
-        <v>0.1115735012934428</v>
+        <v>0.1506203473945409</v>
       </c>
       <c r="X4">
-        <v>0.08798574625341071</v>
+        <v>0.07861655276038142</v>
       </c>
       <c r="Y4">
-        <v>0.02358775504003209</v>
+        <v>0.07200379463415953</v>
       </c>
       <c r="Z4">
-        <v>1.635058738623151</v>
+        <v>2.578536947642035</v>
       </c>
       <c r="AA4">
-        <v>0.1327132031594563</v>
+        <v>0.2228575899050291</v>
       </c>
       <c r="AB4">
-        <v>0.08762650768902425</v>
+        <v>0.07831102458348477</v>
       </c>
       <c r="AC4">
-        <v>0.04508669547043204</v>
+        <v>0.1445465653215443</v>
       </c>
       <c r="AD4">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AG4">
-        <v>-382.5</v>
+        <v>-149.2</v>
       </c>
       <c r="AH4">
-        <v>0.008785529715762273</v>
+        <v>0.00886672208367969</v>
       </c>
       <c r="AI4">
-        <v>0.00550577566663068</v>
+        <v>0.005786095289756803</v>
       </c>
       <c r="AJ4">
-        <v>-1.98289269051322</v>
+        <v>-0.2635111268103144</v>
       </c>
       <c r="AK4">
-        <v>-0.7100426953777612</v>
+        <v>-0.1569700157811678</v>
       </c>
       <c r="AL4">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.37</v>
+        <v>-1.74</v>
       </c>
       <c r="AN4">
-        <v>0.03596614950634696</v>
-      </c>
-      <c r="AO4">
-        <v>366.4864864864865</v>
+        <v>0.03703703703703703</v>
       </c>
       <c r="AP4">
-        <v>-2.697461212976022</v>
+        <v>-0.8634259259259258</v>
       </c>
       <c r="AQ4">
-        <v>366.4864864864865</v>
+        <v>-95.74712643678161</v>
       </c>
     </row>
     <row r="5">
@@ -984,25 +981,28 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.06519999999999999</v>
+        <v>0.00561</v>
+      </c>
+      <c r="E5">
+        <v>-0.183</v>
       </c>
       <c r="G5">
-        <v>-0.01335548172757475</v>
+        <v>-0.04945978391356543</v>
       </c>
       <c r="H5">
-        <v>-0.01335548172757475</v>
+        <v>-0.04945978391356543</v>
       </c>
       <c r="I5">
-        <v>-0.124750830564784</v>
+        <v>0.07466986794717888</v>
       </c>
       <c r="J5">
-        <v>-0.124750830564784</v>
+        <v>0.05568404105828378</v>
       </c>
       <c r="K5">
-        <v>-10.1</v>
+        <v>3.67</v>
       </c>
       <c r="L5">
-        <v>-0.1677740863787375</v>
+        <v>0.04405762304921969</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1011,7 +1011,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1020,79 +1020,79 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>7.61</v>
+        <v>3.39</v>
       </c>
       <c r="V5">
-        <v>0.1406654343807763</v>
+        <v>0.05167682926829269</v>
       </c>
       <c r="W5">
-        <v>-0.07415565345080764</v>
+        <v>0.03276785714285714</v>
       </c>
       <c r="X5">
-        <v>0.08811854642902416</v>
+        <v>0.07935106993102803</v>
       </c>
       <c r="Y5">
-        <v>-0.1622741998798318</v>
+        <v>-0.04658321278817089</v>
       </c>
       <c r="Z5">
-        <v>0.5014159586873231</v>
+        <v>0.8341427756025755</v>
       </c>
       <c r="AA5">
-        <v>-0.06255205730468101</v>
+        <v>0.0464484405651246</v>
       </c>
       <c r="AB5">
-        <v>0.08761449861728104</v>
+        <v>0.07821415765122151</v>
       </c>
       <c r="AC5">
-        <v>-0.150166555921962</v>
+        <v>-0.03176571708609691</v>
       </c>
       <c r="AD5">
-        <v>0.673</v>
+        <v>2.19</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.673</v>
+        <v>2.19</v>
       </c>
       <c r="AG5">
-        <v>-6.937</v>
+        <v>-1.2</v>
       </c>
       <c r="AH5">
-        <v>0.01228707574900042</v>
+        <v>0.03230564980085559</v>
       </c>
       <c r="AI5">
-        <v>0.004978804938856132</v>
+        <v>0.01692557384651055</v>
       </c>
       <c r="AJ5">
-        <v>-0.1470856391662956</v>
+        <v>-0.01863354037267081</v>
       </c>
       <c r="AK5">
-        <v>-0.05438097253905913</v>
+        <v>-0.009523809523809525</v>
       </c>
       <c r="AL5">
-        <v>0.048</v>
+        <v>0.044</v>
       </c>
       <c r="AM5">
-        <v>0.048</v>
+        <v>0.044</v>
       </c>
       <c r="AN5">
-        <v>-0.09628040057224607</v>
+        <v>0.3220588235294118</v>
       </c>
       <c r="AO5">
-        <v>-156.4583333333333</v>
+        <v>141.3636363636364</v>
       </c>
       <c r="AP5">
-        <v>0.99241773962804</v>
+        <v>-0.1764705882352942</v>
       </c>
       <c r="AQ5">
-        <v>-156.4583333333333</v>
+        <v>141.3636363636364</v>
       </c>
     </row>
   </sheetData>
